--- a/Result/profitability/2425.xlsx
+++ b/Result/profitability/2425.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.38</v>
       </c>
       <c r="M2" t="n">
-        <v>0.06625000000000002</v>
+        <v>0.09375</v>
       </c>
       <c r="N2" t="n">
-        <v>6.275</v>
+        <v>6.2925</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.06</v>
       </c>
       <c r="M3" t="n">
-        <v>0.07875000000000001</v>
+        <v>-0.009999999999999995</v>
       </c>
       <c r="N3" t="n">
-        <v>6.315</v>
+        <v>6.32375</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.29</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.05374999999999998</v>
+        <v>-0.08749999999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>6.31875</v>
+        <v>6.31</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-1.18</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.2425</v>
+        <v>-0.01624999999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>5.683750000000001</v>
+        <v>5.845000000000001</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.12</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.008749999999999966</v>
+        <v>-0.06124999999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>6.140000000000001</v>
+        <v>6.06875</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.27</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.03499999999999996</v>
+        <v>-0.105</v>
       </c>
       <c r="N7" t="n">
-        <v>6.35125</v>
+        <v>6.13</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.55</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.04374999999999996</v>
+        <v>-0.11375</v>
       </c>
       <c r="N8" t="n">
-        <v>6.57375</v>
+        <v>6.452500000000001</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1403,7 +1403,7 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R8" t="n">
         <v>1</v>
@@ -1412,7 +1412,7 @@
         <v>1</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
@@ -1518,10 +1518,10 @@
         <v>0.36</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.07624999999999996</v>
+        <v>-0.07624999999999997</v>
       </c>
       <c r="N9" t="n">
-        <v>6.335000000000001</v>
+        <v>6.335</v>
       </c>
       <c r="O9" t="n">
         <v>1</v>
@@ -1645,10 +1645,10 @@
         <v>0.06</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.02124999999999996</v>
+        <v>-0.02124999999999998</v>
       </c>
       <c r="N10" t="n">
-        <v>6.765000000000001</v>
+        <v>6.765</v>
       </c>
       <c r="O10" t="n">
         <v>1</v>
@@ -1772,7 +1772,7 @@
         <v>-0.5</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.07624999999999996</v>
+        <v>-0.07624999999999998</v>
       </c>
       <c r="N11" t="n">
         <v>6.001250000000001</v>
@@ -1902,7 +1902,7 @@
         <v>-0.14375</v>
       </c>
       <c r="N12" t="n">
-        <v>4.7775</v>
+        <v>4.777500000000001</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2425</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>915</v>
+      </c>
+      <c r="D75" t="n">
+        <v>853</v>
+      </c>
+      <c r="E75" t="n">
+        <v>62</v>
+      </c>
+      <c r="F75" t="n">
+        <v>6.73</v>
+      </c>
+      <c r="G75" t="n">
+        <v>10</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>1.10%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-2</v>
+      </c>
+      <c r="J75" t="n">
+        <v>8</v>
+      </c>
+      <c r="K75" t="n">
+        <v>6</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.12125</v>
+      </c>
+      <c r="N75" t="n">
+        <v>6.965000000000001</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.5600000000000001</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.9032258064516129</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-0.9699999999999998</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.125974025974026</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-1.034285714285714</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.2371323529411764</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
